--- a/src/moodys_datahub/data/data_products.xlsx
+++ b/src/moodys_datahub/data/data_products.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://studentcbs-my.sharepoint.com/personal/kgp_lib_cbs_dk/Documents/Desktop/moody-s_datahub/moodys_datahub/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://studentcbs-my.sharepoint.com/personal/kgp_libas_cbs_dk/Documents/Desktop/moody-s_datahub/src/moodys_datahub/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="174" documentId="11_4B0D37945B70D6289F9A3B11595ED87656CCA927" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{072A19C1-F2A3-4D82-B17B-9BB0844E3505}"/>
+  <xr:revisionPtr revIDLastSave="198" documentId="11_4B0D37945B70D6289F9A3B11595ED87656CCA927" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A135FAD7-F0D2-43B4-86F7-CA5EB20C41BC}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1216" uniqueCount="189">
   <si>
     <t>Data Product</t>
   </si>
@@ -70,54 +70,24 @@
     <t>segment_data</t>
   </si>
   <si>
-    <t>banks_global_financials_and_ratios_eur_interim</t>
-  </si>
-  <si>
     <t>4TssGrD7SdCz23qGujJXGQ</t>
   </si>
   <si>
     <t>banks_global_financials_and_ratios_interim</t>
   </si>
   <si>
-    <t>banks_global_financials_and_ratios_usd_interim</t>
-  </si>
-  <si>
-    <t>cash_flow_non_us_industries_eur_interim</t>
-  </si>
-  <si>
     <t>cash_flow_non_us_industries_interim</t>
   </si>
   <si>
-    <t>cash_flow_non_us_industries_usd_interim</t>
-  </si>
-  <si>
-    <t>cash_flow_us_industries_eur_interim</t>
-  </si>
-  <si>
     <t>cash_flow_us_industries_interim</t>
   </si>
   <si>
-    <t>cash_flow_us_industries_usd_interim</t>
-  </si>
-  <si>
-    <t>detailed_format_industries_eur_interim</t>
-  </si>
-  <si>
     <t>detailed_format_industries_interim</t>
   </si>
   <si>
-    <t>detailed_format_industries_usd_interim</t>
-  </si>
-  <si>
-    <t>industry_global_financials_and_ratios_eur_interim</t>
-  </si>
-  <si>
     <t>industry_global_financials_and_ratios_interim</t>
   </si>
   <si>
-    <t>industry_global_financials_and_ratios_usd_interim</t>
-  </si>
-  <si>
     <t>Beneficial Owners (Monthly)</t>
   </si>
   <si>
@@ -584,6 +554,42 @@
   </si>
   <si>
     <t>IlbXwno7RM6H7et71MD3Uw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">banks_global_financials_and_ratios_interim, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">banks_global_financials_and_ratios_interim_usd, </t>
+  </si>
+  <si>
+    <t>banks_global_financials_and_ratios_interim_eur</t>
+  </si>
+  <si>
+    <t>cash_flow_non_us_industries_interim_eur</t>
+  </si>
+  <si>
+    <t>cash_flow_us_industries_interim_eur</t>
+  </si>
+  <si>
+    <t>detailed_format_industries_interim_eur</t>
+  </si>
+  <si>
+    <t>industry_global_financials_and_ratios_interim_eur</t>
+  </si>
+  <si>
+    <t>industry_global_financials_and_ratios_interim_usd</t>
+  </si>
+  <si>
+    <t>banks_global_financials_and_ratios_interim_usd</t>
+  </si>
+  <si>
+    <t>cash_flow_non_us_industries_interim_usd</t>
+  </si>
+  <si>
+    <t>cash_flow_us_industries_interim_usd</t>
+  </si>
+  <si>
+    <t>detailed_format_industries_interim_usd</t>
   </si>
 </sst>
 </file>
@@ -965,7 +971,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E303"/>
+  <dimension ref="A1:L303"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="47.42578125" customWidth="1"/>
@@ -984,7 +990,7 @@
         <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -992,16 +998,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -1009,16 +1015,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="D3" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="E3" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -1026,16 +1032,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="D4" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="E4" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -1043,16 +1049,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="D5" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="E5" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -1060,16 +1066,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="D6" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="E6" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -1077,16 +1083,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="D7" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="E7" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -1094,16 +1100,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="D8" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="E8" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -1111,16 +1117,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="D9" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="E9" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -1128,16 +1134,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="D10" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="E10" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -1145,16 +1151,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="D11" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="E11" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -1162,16 +1168,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="D12" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="E12" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -1179,16 +1185,16 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="C13" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D13" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="E13" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -1196,16 +1202,16 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="C14" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D14" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="E14" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -1213,16 +1219,16 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D15" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="E15" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -1230,16 +1236,16 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="C16" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="D16" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="E16" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -1247,16 +1253,16 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="C17" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D17" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="E17" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -1264,16 +1270,16 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="C18" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="D18" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="E18" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -1281,16 +1287,16 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="C19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="D19" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="E19" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -1298,16 +1304,16 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="C20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="D20" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="E20" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -1315,16 +1321,16 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="C21" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D21" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="E21" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -1332,16 +1338,16 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="C22" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="D22" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E22" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -1349,16 +1355,16 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="C23" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="D23" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E23" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -1366,16 +1372,16 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C24" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D24" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E24" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -1383,16 +1389,16 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C25" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="D25" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E25" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -1400,16 +1406,16 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="C26" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D26" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="E26" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -1417,16 +1423,16 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="C27" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D27" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="E27" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -1434,16 +1440,16 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="C28" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D28" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="E28" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -1451,16 +1457,16 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="C29" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="D29" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="E29" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -1468,16 +1474,16 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="C30" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D30" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="E30" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -1485,16 +1491,16 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="C31" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="D31" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="E31" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -1502,16 +1508,16 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="C32" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="D32" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="E32" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1519,16 +1525,16 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="C33" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="D33" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="E33" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -1536,16 +1542,16 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="C34" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D34" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="E34" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -1553,16 +1559,16 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="C35" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="D35" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="E35" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -1570,16 +1576,16 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="C36" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D36" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="E36" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -1587,16 +1593,16 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="C37" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D37" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="E37" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -1604,16 +1610,16 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="C38" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D38" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="E38" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -1621,16 +1627,16 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="C39" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="D39" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="E39" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -1638,16 +1644,16 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="C40" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="D40" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="E40" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -1655,16 +1661,16 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="C41" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="D41" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="E41" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -1672,16 +1678,16 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="C42" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="D42" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="E42" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -1689,16 +1695,16 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="C43" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="D43" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="E43" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -1706,16 +1712,16 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="C44" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D44" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="E44" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -1723,16 +1729,16 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="C45" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="D45" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="E45" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -1740,16 +1746,16 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="C46" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="D46" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="E46" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -1757,16 +1763,16 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C47" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D47" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E47" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -1774,16 +1780,16 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C48" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="D48" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E48" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -1791,16 +1797,16 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C49" t="s">
+        <v>42</v>
+      </c>
+      <c r="D49" t="s">
         <v>52</v>
       </c>
-      <c r="D49" t="s">
-        <v>62</v>
-      </c>
       <c r="E49" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -1808,16 +1814,16 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C50" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="D50" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E50" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -1825,16 +1831,16 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C51" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="D51" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E51" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -1842,16 +1848,16 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C52" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="D52" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E52" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -1859,16 +1865,16 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C53" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D53" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E53" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -1876,16 +1882,16 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C54" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="D54" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E54" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -1893,16 +1899,16 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C55" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="D55" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E55" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -1910,16 +1916,16 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="C56" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="D56" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="E56" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -1927,16 +1933,16 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="C57" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="D57" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="E57" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -1944,16 +1950,16 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="C58" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="D58" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="E58" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -1961,16 +1967,16 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="C59" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="D59" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="E59" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -1978,16 +1984,16 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C60" t="s">
+        <v>179</v>
+      </c>
+      <c r="D60" t="s">
         <v>15</v>
       </c>
-      <c r="D60" t="s">
-        <v>16</v>
-      </c>
       <c r="E60" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -1995,16 +2001,16 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C61" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D61" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E61" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -2012,16 +2018,16 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C62" t="s">
-        <v>18</v>
+        <v>185</v>
       </c>
       <c r="D62" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E62" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
@@ -2029,16 +2035,16 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C63" t="s">
-        <v>19</v>
+        <v>180</v>
       </c>
       <c r="D63" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E63" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -2046,16 +2052,16 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C64" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D64" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E64" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
@@ -2063,16 +2069,16 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C65" t="s">
-        <v>21</v>
+        <v>186</v>
       </c>
       <c r="D65" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E65" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -2080,16 +2086,16 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C66" t="s">
-        <v>22</v>
+        <v>181</v>
       </c>
       <c r="D66" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E66" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
@@ -2097,16 +2103,16 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C67" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D67" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E67" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
@@ -2114,16 +2120,16 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C68" t="s">
-        <v>24</v>
+        <v>187</v>
       </c>
       <c r="D68" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E68" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
@@ -2131,16 +2137,16 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C69" t="s">
-        <v>25</v>
+        <v>182</v>
       </c>
       <c r="D69" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E69" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
@@ -2148,16 +2154,16 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C70" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D70" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E70" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -2165,16 +2171,16 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C71" t="s">
-        <v>27</v>
+        <v>188</v>
       </c>
       <c r="D71" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E71" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -2182,16 +2188,16 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C72" t="s">
-        <v>28</v>
+        <v>183</v>
       </c>
       <c r="D72" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E72" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -2199,16 +2205,16 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C73" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D73" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E73" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -2216,16 +2222,16 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C74" t="s">
-        <v>30</v>
+        <v>184</v>
       </c>
       <c r="D74" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E74" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -2233,16 +2239,16 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="C75" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="D75" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="E75" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -2250,16 +2256,16 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="C76" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D76" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="E76" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -2267,16 +2273,16 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="C77" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D77" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="E77" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
@@ -2284,16 +2290,16 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C78" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="D78" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="E78" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -2301,16 +2307,16 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C79" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="D79" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="E79" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
@@ -2318,16 +2324,16 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C80" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D80" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="E80" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -2335,16 +2341,16 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C81" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="D81" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="E81" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -2352,16 +2358,16 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="D82" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="E82" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
@@ -2369,16 +2375,16 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C83" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="D83" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="E83" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
@@ -2395,7 +2401,7 @@
         <v>5</v>
       </c>
       <c r="E84" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -2412,7 +2418,7 @@
         <v>5</v>
       </c>
       <c r="E85" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -2429,7 +2435,7 @@
         <v>5</v>
       </c>
       <c r="E86" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
@@ -2446,7 +2452,7 @@
         <v>5</v>
       </c>
       <c r="E87" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
@@ -2463,7 +2469,7 @@
         <v>5</v>
       </c>
       <c r="E88" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
@@ -2480,7 +2486,7 @@
         <v>5</v>
       </c>
       <c r="E89" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -2497,7 +2503,7 @@
         <v>5</v>
       </c>
       <c r="E90" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
@@ -2514,7 +2520,7 @@
         <v>5</v>
       </c>
       <c r="E91" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
@@ -2531,7 +2537,7 @@
         <v>5</v>
       </c>
       <c r="E92" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
@@ -2548,7 +2554,7 @@
         <v>5</v>
       </c>
       <c r="E93" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
@@ -2556,16 +2562,16 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="C94" t="s">
         <v>4</v>
       </c>
       <c r="D94" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="E94" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
@@ -2573,16 +2579,16 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="C95" t="s">
         <v>6</v>
       </c>
       <c r="D95" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="E95" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -2590,16 +2596,16 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="C96" t="s">
         <v>7</v>
       </c>
       <c r="D96" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="E96" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
@@ -2607,16 +2613,16 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="C97" t="s">
         <v>8</v>
       </c>
       <c r="D97" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="E97" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
@@ -2624,16 +2630,16 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="C98" t="s">
         <v>9</v>
       </c>
       <c r="D98" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="E98" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
@@ -2641,16 +2647,16 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="C99" t="s">
         <v>10</v>
       </c>
       <c r="D99" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="E99" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
@@ -2658,16 +2664,16 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="C100" t="s">
         <v>11</v>
       </c>
       <c r="D100" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="E100" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
@@ -2675,16 +2681,16 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="C101" t="s">
         <v>12</v>
       </c>
       <c r="D101" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="E101" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
@@ -2692,16 +2698,16 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="C102" t="s">
         <v>13</v>
       </c>
       <c r="D102" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="E102" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
@@ -2709,16 +2715,16 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="C103" t="s">
         <v>14</v>
       </c>
       <c r="D103" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="E103" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
@@ -2726,16 +2732,16 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C104" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="D104" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="E104" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
@@ -2743,16 +2749,16 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C105" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="D105" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="E105" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
@@ -2760,16 +2766,16 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C106" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="D106" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="E106" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
@@ -2777,16 +2783,16 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C107" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="D107" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="E107" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
@@ -2794,16 +2800,16 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C108" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="D108" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="E108" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
@@ -2811,16 +2817,16 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C109" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="D109" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="E109" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
@@ -2828,16 +2834,16 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C110" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D110" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="E110" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
@@ -2845,16 +2851,16 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C111" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D111" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="E111" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
@@ -2862,16 +2868,16 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C112" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="D112" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="E112" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
@@ -2879,16 +2885,16 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C113" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D113" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="E113" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
@@ -2896,16 +2902,16 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C114" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="D114" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="E114" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
@@ -2913,16 +2919,16 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C115" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="D115" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="E115" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
@@ -2930,16 +2936,16 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C116" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D116" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="E116" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
@@ -2947,16 +2953,16 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C117" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="D117" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="E117" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
@@ -2964,16 +2970,16 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C118" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="D118" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="E118" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
@@ -2981,16 +2987,16 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C119" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="D119" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="E119" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
@@ -2998,16 +3004,16 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C120" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D120" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="E120" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
@@ -3015,16 +3021,16 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C121" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="D121" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="E121" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
@@ -3032,16 +3038,16 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="C122" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="D122" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="E122" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
@@ -3049,16 +3055,16 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="C123" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="D123" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="E123" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
@@ -3066,16 +3072,16 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="C124" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="D124" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="E124" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
@@ -3083,16 +3089,16 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="C125" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="D125" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="E125" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
@@ -3100,16 +3106,16 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="C126" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="D126" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="E126" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
@@ -3117,16 +3123,16 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="C127" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="D127" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="E127" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
@@ -3134,16 +3140,16 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="C128" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="D128" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E128" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
@@ -3151,16 +3157,16 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="C129" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="D129" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E129" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
@@ -3168,16 +3174,16 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="C130" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="D130" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E130" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
@@ -3185,16 +3191,16 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="C131" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="D131" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E131" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
@@ -3202,16 +3208,16 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="C132" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="D132" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E132" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
@@ -3219,16 +3225,16 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C133" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="D133" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E133" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
@@ -3236,16 +3242,16 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C134" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D134" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E134" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
@@ -3253,16 +3259,16 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C135" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="D135" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E135" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
@@ -3270,16 +3276,16 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C136" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="D136" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E136" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
@@ -3287,16 +3293,16 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C137" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="D137" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E137" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="138" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3304,16 +3310,16 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C138" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="D138" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E138" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
@@ -3321,16 +3327,16 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C139" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="D139" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E139" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
@@ -3338,16 +3344,16 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C140" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="D140" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E140" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
@@ -3355,16 +3361,16 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
+        <v>57</v>
+      </c>
+      <c r="C141" t="s">
         <v>67</v>
       </c>
-      <c r="C141" t="s">
-        <v>77</v>
-      </c>
       <c r="D141" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E141" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
@@ -3372,16 +3378,16 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C142" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D142" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E142" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
@@ -3389,16 +3395,16 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C143" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D143" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E143" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
@@ -3406,16 +3412,16 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C144" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D144" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E144" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
@@ -3423,16 +3429,16 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C145" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="D145" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E145" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
@@ -3440,16 +3446,16 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C146" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D146" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E146" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
@@ -3457,16 +3463,16 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C147" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D147" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E147" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
@@ -3474,16 +3480,16 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C148" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="D148" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E148" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
@@ -3491,16 +3497,16 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C149" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="D149" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E149" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
@@ -3508,16 +3514,16 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C150" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="D150" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E150" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
@@ -3525,16 +3531,16 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="C151" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="D151" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="E151" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
@@ -3542,16 +3548,16 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="C152" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="D152" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="E152" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
@@ -3559,16 +3565,16 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="C153" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="D153" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="E153" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
@@ -3576,16 +3582,16 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="C154" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="D154" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="E154" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
@@ -3593,16 +3599,16 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="C155" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D155" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="E155" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
@@ -3610,16 +3616,16 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="C156" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D156" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="E156" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
@@ -3627,16 +3633,16 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="C157" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="D157" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="E157" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
@@ -3644,16 +3650,16 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="C158" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="D158" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="E158" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
@@ -3661,16 +3667,16 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="C159" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="D159" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="E159" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
@@ -3678,16 +3684,16 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="C160" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="D160" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="E160" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
@@ -3695,16 +3701,16 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="C161" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="D161" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="E161" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
@@ -3712,16 +3718,16 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="C162" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="D162" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="E162" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
@@ -3729,16 +3735,16 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C163" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="D163" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="E163" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
@@ -3746,16 +3752,16 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C164" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D164" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="E164" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
@@ -3763,16 +3769,16 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C165" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="D165" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="E165" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
@@ -3780,16 +3786,16 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C166" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="D166" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="E166" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
@@ -3797,16 +3803,16 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C167" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="D167" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="E167" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
@@ -3814,16 +3820,16 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C168" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="D168" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="E168" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
@@ -3831,16 +3837,16 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C169" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="D169" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="E169" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
@@ -3848,16 +3854,16 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C170" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="D170" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="E170" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
@@ -3865,16 +3871,16 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
+        <v>57</v>
+      </c>
+      <c r="C171" t="s">
         <v>67</v>
       </c>
-      <c r="C171" t="s">
-        <v>77</v>
-      </c>
       <c r="D171" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="E171" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
@@ -3882,16 +3888,16 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C172" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D172" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="E172" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
@@ -3899,16 +3905,16 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C173" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D173" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="E173" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
@@ -3916,16 +3922,16 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C174" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D174" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="E174" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
@@ -3933,16 +3939,16 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C175" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="D175" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="E175" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
@@ -3950,16 +3956,16 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C176" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D176" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="E176" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
@@ -3967,16 +3973,16 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C177" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D177" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="E177" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
@@ -3984,16 +3990,16 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C178" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="D178" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="E178" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
@@ -4001,16 +4007,16 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C179" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="D179" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="E179" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
@@ -4018,16 +4024,16 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C180" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="D180" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="E180" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
@@ -4035,16 +4041,16 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C181" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D181" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="E181" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
@@ -4052,16 +4058,16 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="C182" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="D182" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="E182" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
@@ -4069,16 +4075,16 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="C183" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="D183" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="E183" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
@@ -4086,16 +4092,16 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="C184" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="D184" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="E184" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
@@ -4103,16 +4109,16 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="C185" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="D185" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="E185" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
@@ -4126,10 +4132,10 @@
         <v>4</v>
       </c>
       <c r="D186" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="E186" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
@@ -4143,10 +4149,10 @@
         <v>6</v>
       </c>
       <c r="D187" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="E187" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
@@ -4160,10 +4166,10 @@
         <v>7</v>
       </c>
       <c r="D188" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="E188" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
@@ -4177,10 +4183,10 @@
         <v>8</v>
       </c>
       <c r="D189" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="E189" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
@@ -4194,10 +4200,10 @@
         <v>9</v>
       </c>
       <c r="D190" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="E190" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
@@ -4211,10 +4217,10 @@
         <v>10</v>
       </c>
       <c r="D191" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="E191" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
@@ -4228,10 +4234,10 @@
         <v>11</v>
       </c>
       <c r="D192" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="E192" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
@@ -4245,10 +4251,10 @@
         <v>12</v>
       </c>
       <c r="D193" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="E193" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.25">
@@ -4262,10 +4268,10 @@
         <v>13</v>
       </c>
       <c r="D194" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="E194" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.25">
@@ -4279,10 +4285,10 @@
         <v>14</v>
       </c>
       <c r="D195" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="E195" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.25">
@@ -4290,16 +4296,16 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C196" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="D196" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="E196" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.25">
@@ -4307,16 +4313,16 @@
         <v>196</v>
       </c>
       <c r="B197" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C197" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="D197" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="E197" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.25">
@@ -4324,16 +4330,16 @@
         <v>197</v>
       </c>
       <c r="B198" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C198" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D198" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="E198" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.25">
@@ -4341,16 +4347,16 @@
         <v>198</v>
       </c>
       <c r="B199" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C199" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="D199" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="E199" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
@@ -4358,16 +4364,16 @@
         <v>199</v>
       </c>
       <c r="B200" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C200" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="D200" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="E200" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.25">
@@ -4375,16 +4381,16 @@
         <v>200</v>
       </c>
       <c r="B201" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C201" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="D201" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="E201" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.25">
@@ -4392,16 +4398,16 @@
         <v>201</v>
       </c>
       <c r="B202" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C202" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D202" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="E202" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.25">
@@ -4409,16 +4415,16 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C203" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="D203" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="E203" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.25">
@@ -4426,16 +4432,16 @@
         <v>203</v>
       </c>
       <c r="B204" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C204" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="D204" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="E204" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.25">
@@ -4443,16 +4449,16 @@
         <v>204</v>
       </c>
       <c r="B205" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C205" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="D205" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="E205" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.25">
@@ -4460,16 +4466,16 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C206" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="D206" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="E206" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.25">
@@ -4477,16 +4483,16 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C207" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="D207" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="E207" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
@@ -4494,16 +4500,16 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C208" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D208" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="E208" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.25">
@@ -4511,16 +4517,16 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C209" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="D209" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="E209" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
@@ -4528,16 +4534,16 @@
         <v>209</v>
       </c>
       <c r="B210" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C210" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="D210" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="E210" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.25">
@@ -4545,16 +4551,16 @@
         <v>210</v>
       </c>
       <c r="B211" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="C211" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="D211" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E211" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.25">
@@ -4562,16 +4568,16 @@
         <v>211</v>
       </c>
       <c r="B212" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="C212" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="D212" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E212" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
@@ -4579,16 +4585,16 @@
         <v>212</v>
       </c>
       <c r="B213" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="C213" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="D213" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E213" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
@@ -4596,16 +4602,16 @@
         <v>213</v>
       </c>
       <c r="B214" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="C214" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="D214" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E214" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
@@ -4613,16 +4619,16 @@
         <v>214</v>
       </c>
       <c r="B215" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="C215" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="D215" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E215" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
@@ -4630,16 +4636,16 @@
         <v>215</v>
       </c>
       <c r="B216" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="C216" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="D216" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="E216" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.25">
@@ -4647,16 +4653,16 @@
         <v>216</v>
       </c>
       <c r="B217" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="C217" t="s">
         <v>4</v>
       </c>
       <c r="D217" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="E217" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.25">
@@ -4664,16 +4670,16 @@
         <v>217</v>
       </c>
       <c r="B218" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="C218" t="s">
         <v>6</v>
       </c>
       <c r="D218" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="E218" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
@@ -4681,16 +4687,16 @@
         <v>218</v>
       </c>
       <c r="B219" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="C219" t="s">
         <v>7</v>
       </c>
       <c r="D219" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="E219" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.25">
@@ -4698,16 +4704,16 @@
         <v>219</v>
       </c>
       <c r="B220" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="C220" t="s">
         <v>8</v>
       </c>
       <c r="D220" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="E220" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.25">
@@ -4715,16 +4721,16 @@
         <v>220</v>
       </c>
       <c r="B221" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="C221" t="s">
         <v>9</v>
       </c>
       <c r="D221" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="E221" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
@@ -4732,16 +4738,16 @@
         <v>221</v>
       </c>
       <c r="B222" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="C222" t="s">
         <v>10</v>
       </c>
       <c r="D222" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="E222" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
@@ -4749,16 +4755,16 @@
         <v>222</v>
       </c>
       <c r="B223" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="C223" t="s">
         <v>11</v>
       </c>
       <c r="D223" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="E223" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
@@ -4766,288 +4772,300 @@
         <v>223</v>
       </c>
       <c r="B224" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="C224" t="s">
         <v>12</v>
       </c>
       <c r="D224" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="E224" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="225" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A225" s="1">
         <v>224</v>
       </c>
       <c r="B225" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="C225" t="s">
         <v>13</v>
       </c>
       <c r="D225" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="E225" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="226" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A226" s="1">
         <v>225</v>
       </c>
       <c r="B226" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="C226" t="s">
         <v>14</v>
       </c>
       <c r="D226" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="E226" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="227" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A227" s="1">
         <v>226</v>
       </c>
       <c r="B227" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C227" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D227" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="E227" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+      <c r="L227" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="228" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A228" s="1">
         <v>227</v>
       </c>
       <c r="B228" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C228" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="D228" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="E228" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+      <c r="L228" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="229" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A229" s="1">
         <v>228</v>
       </c>
       <c r="B229" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C229" t="s">
-        <v>15</v>
+        <v>179</v>
       </c>
       <c r="D229" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="E229" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+      <c r="L229" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="230" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A230" s="1">
         <v>229</v>
       </c>
       <c r="B230" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C230" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D230" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="E230" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+      <c r="L230" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="231" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A231" s="1">
         <v>230</v>
       </c>
       <c r="B231" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C231" t="s">
-        <v>18</v>
+        <v>185</v>
       </c>
       <c r="D231" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="E231" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="232" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A232" s="1">
         <v>231</v>
       </c>
       <c r="B232" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C232" t="s">
-        <v>19</v>
+        <v>180</v>
       </c>
       <c r="D232" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="E232" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="233" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A233" s="1">
         <v>232</v>
       </c>
       <c r="B233" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C233" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D233" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="E233" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="234" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A234" s="1">
         <v>233</v>
       </c>
       <c r="B234" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C234" t="s">
-        <v>21</v>
+        <v>186</v>
       </c>
       <c r="D234" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="E234" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="235" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A235" s="1">
         <v>234</v>
       </c>
       <c r="B235" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C235" t="s">
-        <v>22</v>
+        <v>181</v>
       </c>
       <c r="D235" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="E235" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="236" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A236" s="1">
         <v>235</v>
       </c>
       <c r="B236" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C236" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D236" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="E236" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="237" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A237" s="1">
         <v>236</v>
       </c>
       <c r="B237" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C237" t="s">
-        <v>24</v>
+        <v>187</v>
       </c>
       <c r="D237" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="E237" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="238" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A238" s="1">
         <v>237</v>
       </c>
       <c r="B238" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C238" t="s">
-        <v>25</v>
+        <v>182</v>
       </c>
       <c r="D238" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="E238" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="239" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A239" s="1">
         <v>238</v>
       </c>
       <c r="B239" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C239" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D239" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="E239" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="240" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A240" s="1">
         <v>239</v>
       </c>
       <c r="B240" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C240" t="s">
-        <v>27</v>
+        <v>188</v>
       </c>
       <c r="D240" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="E240" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.25">
@@ -5055,16 +5073,16 @@
         <v>240</v>
       </c>
       <c r="B241" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C241" t="s">
-        <v>28</v>
+        <v>183</v>
       </c>
       <c r="D241" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="E241" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.25">
@@ -5072,16 +5090,16 @@
         <v>241</v>
       </c>
       <c r="B242" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C242" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D242" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="E242" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.25">
@@ -5089,16 +5107,16 @@
         <v>242</v>
       </c>
       <c r="B243" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C243" t="s">
-        <v>30</v>
+        <v>184</v>
       </c>
       <c r="D243" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="E243" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.25">
@@ -5106,16 +5124,16 @@
         <v>243</v>
       </c>
       <c r="B244" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="C244" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D244" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="E244" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.25">
@@ -5123,16 +5141,16 @@
         <v>244</v>
       </c>
       <c r="B245" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="C245" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D245" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="E245" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.25">
@@ -5140,16 +5158,16 @@
         <v>245</v>
       </c>
       <c r="B246" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="C246" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D246" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="E246" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.25">
@@ -5157,16 +5175,16 @@
         <v>246</v>
       </c>
       <c r="B247" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="C247" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="D247" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="E247" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.25">
@@ -5174,16 +5192,16 @@
         <v>247</v>
       </c>
       <c r="B248" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="C248" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D248" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="E248" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.25">
@@ -5191,16 +5209,16 @@
         <v>248</v>
       </c>
       <c r="B249" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="C249" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="D249" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="E249" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.25">
@@ -5208,16 +5226,16 @@
         <v>249</v>
       </c>
       <c r="B250" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="C250" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="D250" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="E250" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.25">
@@ -5225,16 +5243,16 @@
         <v>250</v>
       </c>
       <c r="B251" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="C251" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="D251" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="E251" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.25">
@@ -5242,16 +5260,16 @@
         <v>251</v>
       </c>
       <c r="B252" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="C252" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D252" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="E252" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.25">
@@ -5259,16 +5277,16 @@
         <v>252</v>
       </c>
       <c r="B253" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="C253" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="D253" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="E253" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.25">
@@ -5276,16 +5294,16 @@
         <v>253</v>
       </c>
       <c r="B254" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="C254" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D254" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="E254" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.25">
@@ -5293,16 +5311,16 @@
         <v>254</v>
       </c>
       <c r="B255" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="C255" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D255" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="E255" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.25">
@@ -5310,16 +5328,16 @@
         <v>255</v>
       </c>
       <c r="B256" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="C256" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D256" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="E256" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.25">
@@ -5327,16 +5345,16 @@
         <v>256</v>
       </c>
       <c r="B257" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="C257" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="D257" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="E257" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.25">
@@ -5344,16 +5362,16 @@
         <v>257</v>
       </c>
       <c r="B258" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="C258" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="D258" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="E258" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.25">
@@ -5361,16 +5379,16 @@
         <v>258</v>
       </c>
       <c r="B259" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="C259" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="D259" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="E259" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.25">
@@ -5378,16 +5396,16 @@
         <v>259</v>
       </c>
       <c r="B260" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="C260" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="D260" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="E260" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.25">
@@ -5395,16 +5413,16 @@
         <v>260</v>
       </c>
       <c r="B261" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="C261" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="D261" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="E261" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.25">
@@ -5412,16 +5430,16 @@
         <v>261</v>
       </c>
       <c r="B262" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="C262" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D262" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="E262" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.25">
@@ -5429,16 +5447,16 @@
         <v>262</v>
       </c>
       <c r="B263" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="C263" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="D263" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="E263" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.25">
@@ -5446,16 +5464,16 @@
         <v>263</v>
       </c>
       <c r="B264" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="C264" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="D264" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="E264" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.25">
@@ -5463,16 +5481,16 @@
         <v>264</v>
       </c>
       <c r="B265" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C265" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="D265" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="E265" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.25">
@@ -5480,16 +5498,16 @@
         <v>265</v>
       </c>
       <c r="B266" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C266" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="D266" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="E266" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.25">
@@ -5497,16 +5515,16 @@
         <v>266</v>
       </c>
       <c r="B267" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C267" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="D267" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="E267" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.25">
@@ -5514,16 +5532,16 @@
         <v>267</v>
       </c>
       <c r="B268" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C268" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="D268" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="E268" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.25">
@@ -5531,16 +5549,16 @@
         <v>268</v>
       </c>
       <c r="B269" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C269" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="D269" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="E269" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.25">
@@ -5548,16 +5566,16 @@
         <v>269</v>
       </c>
       <c r="B270" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C270" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="D270" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="E270" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.25">
@@ -5565,16 +5583,16 @@
         <v>270</v>
       </c>
       <c r="B271" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C271" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D271" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="E271" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.25">
@@ -5582,16 +5600,16 @@
         <v>271</v>
       </c>
       <c r="B272" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C272" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D272" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="E272" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.25">
@@ -5599,16 +5617,16 @@
         <v>272</v>
       </c>
       <c r="B273" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C273" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="D273" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="E273" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.25">
@@ -5616,16 +5634,16 @@
         <v>273</v>
       </c>
       <c r="B274" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C274" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D274" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="E274" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.25">
@@ -5633,16 +5651,16 @@
         <v>274</v>
       </c>
       <c r="B275" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C275" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="D275" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="E275" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.25">
@@ -5650,16 +5668,16 @@
         <v>275</v>
       </c>
       <c r="B276" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C276" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="D276" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="E276" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.25">
@@ -5667,16 +5685,16 @@
         <v>276</v>
       </c>
       <c r="B277" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C277" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D277" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="E277" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.25">
@@ -5684,16 +5702,16 @@
         <v>277</v>
       </c>
       <c r="B278" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C278" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="D278" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="E278" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.25">
@@ -5701,16 +5719,16 @@
         <v>278</v>
       </c>
       <c r="B279" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C279" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="D279" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="E279" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.25">
@@ -5718,16 +5736,16 @@
         <v>279</v>
       </c>
       <c r="B280" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C280" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="D280" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="E280" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.25">
@@ -5735,16 +5753,16 @@
         <v>280</v>
       </c>
       <c r="B281" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C281" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D281" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="E281" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.25">
@@ -5752,16 +5770,16 @@
         <v>281</v>
       </c>
       <c r="B282" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C282" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="D282" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="E282" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.25">
@@ -5769,16 +5787,16 @@
         <v>282</v>
       </c>
       <c r="B283" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="C283" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D283" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="E283" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.25">
@@ -5786,16 +5804,16 @@
         <v>283</v>
       </c>
       <c r="B284" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="C284" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D284" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="E284" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.25">
@@ -5803,16 +5821,16 @@
         <v>284</v>
       </c>
       <c r="B285" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="C285" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D285" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="E285" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.25">
@@ -5820,16 +5838,16 @@
         <v>285</v>
       </c>
       <c r="B286" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="C286" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="D286" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="E286" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.25">
@@ -5837,16 +5855,16 @@
         <v>286</v>
       </c>
       <c r="B287" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="C287" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D287" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="E287" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.25">
@@ -5854,16 +5872,16 @@
         <v>287</v>
       </c>
       <c r="B288" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="C288" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="D288" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="E288" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.25">
@@ -5871,16 +5889,16 @@
         <v>288</v>
       </c>
       <c r="B289" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="C289" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="D289" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="E289" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.25">
@@ -5888,16 +5906,16 @@
         <v>289</v>
       </c>
       <c r="B290" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="C290" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="D290" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="E290" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.25">
@@ -5905,16 +5923,16 @@
         <v>290</v>
       </c>
       <c r="B291" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="C291" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D291" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="E291" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.25">
@@ -5922,16 +5940,16 @@
         <v>291</v>
       </c>
       <c r="B292" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C292" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="D292" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="E292" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.25">
@@ -5939,16 +5957,16 @@
         <v>292</v>
       </c>
       <c r="B293" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C293" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="D293" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="E293" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.25">
@@ -5956,16 +5974,16 @@
         <v>293</v>
       </c>
       <c r="B294" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C294" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="D294" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="E294" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.25">
@@ -5973,16 +5991,16 @@
         <v>294</v>
       </c>
       <c r="B295" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C295" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="D295" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="E295" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.25">
@@ -5990,16 +6008,16 @@
         <v>295</v>
       </c>
       <c r="B296" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C296" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="D296" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="E296" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.25">
@@ -6007,16 +6025,16 @@
         <v>296</v>
       </c>
       <c r="B297" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C297" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="D297" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="E297" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.25">
@@ -6024,16 +6042,16 @@
         <v>297</v>
       </c>
       <c r="B298" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C298" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="D298" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="E298" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.25">
@@ -6041,16 +6059,16 @@
         <v>298</v>
       </c>
       <c r="B299" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C299" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="D299" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="E299" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.25">
@@ -6058,16 +6076,16 @@
         <v>299</v>
       </c>
       <c r="B300" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C300" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="D300" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="E300" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.25">
@@ -6075,16 +6093,16 @@
         <v>300</v>
       </c>
       <c r="B301" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="C301" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="D301" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="E301" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.25">
@@ -6092,16 +6110,16 @@
         <v>301</v>
       </c>
       <c r="B302" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="C302" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="D302" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="E302" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.25">
@@ -6109,16 +6127,16 @@
         <v>302</v>
       </c>
       <c r="B303" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="C303" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="D303" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="E303" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>

--- a/src/moodys_datahub/data/data_products.xlsx
+++ b/src/moodys_datahub/data/data_products.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://studentcbs-my.sharepoint.com/personal/kgp_libas_cbs_dk/Documents/Desktop/moody-s_datahub/src/moodys_datahub/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="198" documentId="11_4B0D37945B70D6289F9A3B11595ED87656CCA927" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A135FAD7-F0D2-43B4-86F7-CA5EB20C41BC}"/>
+  <xr:revisionPtr revIDLastSave="201" documentId="11_4B0D37945B70D6289F9A3B11595ED87656CCA927" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4AB658DE-89D0-4232-A8F1-C0DBD8107F81}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$301</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$303</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1216" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1216" uniqueCount="190">
   <si>
     <t>Data Product</t>
   </si>
@@ -590,6 +590,9 @@
   </si>
   <si>
     <t>detailed_format_industries_interim_usd</t>
+  </si>
+  <si>
+    <t>status_history</t>
   </si>
 </sst>
 </file>
@@ -5450,7 +5453,7 @@
         <v>132</v>
       </c>
       <c r="C263" t="s">
-        <v>47</v>
+        <v>189</v>
       </c>
       <c r="D263" t="s">
         <v>162</v>
@@ -6140,7 +6143,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E301" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <autoFilter ref="A1:E303" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E301">
       <sortCondition ref="A1:A301"/>
     </sortState>

--- a/src/moodys_datahub/data/data_products.xlsx
+++ b/src/moodys_datahub/data/data_products.xlsx
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://studentcbs-my.sharepoint.com/personal/kgp_libas_cbs_dk/Documents/Desktop/moody-s_datahub/src/moodys_datahub/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="201" documentId="11_4B0D37945B70D6289F9A3B11595ED87656CCA927" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4AB658DE-89D0-4232-A8F1-C0DBD8107F81}"/>
+  <xr:revisionPtr revIDLastSave="215" documentId="11_4B0D37945B70D6289F9A3B11595ED87656CCA927" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71EEC99A-F9A2-4C00-A708-B204118AEE55}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6030" yWindow="4815" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$303</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$305</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1216" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1224" uniqueCount="191">
   <si>
     <t>Data Product</t>
   </si>
@@ -593,6 +593,9 @@
   </si>
   <si>
     <t>status_history</t>
+  </si>
+  <si>
+    <t>orbis_monthly_shareholders_bvdid_uci</t>
   </si>
 </sst>
 </file>
@@ -974,7 +977,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L303"/>
+  <dimension ref="A1:L305"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="47.42578125" customWidth="1"/>
@@ -2395,13 +2398,13 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="C84" t="s">
-        <v>4</v>
+        <v>190</v>
       </c>
       <c r="D84" t="s">
-        <v>5</v>
+        <v>82</v>
       </c>
       <c r="E84" t="s">
         <v>146</v>
@@ -2415,7 +2418,7 @@
         <v>3</v>
       </c>
       <c r="C85" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D85" t="s">
         <v>5</v>
@@ -2432,7 +2435,7 @@
         <v>3</v>
       </c>
       <c r="C86" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D86" t="s">
         <v>5</v>
@@ -2449,7 +2452,7 @@
         <v>3</v>
       </c>
       <c r="C87" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D87" t="s">
         <v>5</v>
@@ -2466,7 +2469,7 @@
         <v>3</v>
       </c>
       <c r="C88" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D88" t="s">
         <v>5</v>
@@ -2483,7 +2486,7 @@
         <v>3</v>
       </c>
       <c r="C89" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D89" t="s">
         <v>5</v>
@@ -2500,7 +2503,7 @@
         <v>3</v>
       </c>
       <c r="C90" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D90" t="s">
         <v>5</v>
@@ -2517,7 +2520,7 @@
         <v>3</v>
       </c>
       <c r="C91" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D91" t="s">
         <v>5</v>
@@ -2534,7 +2537,7 @@
         <v>3</v>
       </c>
       <c r="C92" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D92" t="s">
         <v>5</v>
@@ -2551,7 +2554,7 @@
         <v>3</v>
       </c>
       <c r="C93" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D93" t="s">
         <v>5</v>
@@ -2565,13 +2568,13 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>133</v>
+        <v>3</v>
       </c>
       <c r="C94" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D94" t="s">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="E94" t="s">
         <v>146</v>
@@ -2585,7 +2588,7 @@
         <v>133</v>
       </c>
       <c r="C95" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D95" t="s">
         <v>38</v>
@@ -2602,7 +2605,7 @@
         <v>133</v>
       </c>
       <c r="C96" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D96" t="s">
         <v>38</v>
@@ -2619,7 +2622,7 @@
         <v>133</v>
       </c>
       <c r="C97" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D97" t="s">
         <v>38</v>
@@ -2636,7 +2639,7 @@
         <v>133</v>
       </c>
       <c r="C98" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D98" t="s">
         <v>38</v>
@@ -2653,7 +2656,7 @@
         <v>133</v>
       </c>
       <c r="C99" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D99" t="s">
         <v>38</v>
@@ -2670,7 +2673,7 @@
         <v>133</v>
       </c>
       <c r="C100" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D100" t="s">
         <v>38</v>
@@ -2687,7 +2690,7 @@
         <v>133</v>
       </c>
       <c r="C101" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D101" t="s">
         <v>38</v>
@@ -2704,7 +2707,7 @@
         <v>133</v>
       </c>
       <c r="C102" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D102" t="s">
         <v>38</v>
@@ -2721,7 +2724,7 @@
         <v>133</v>
       </c>
       <c r="C103" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D103" t="s">
         <v>38</v>
@@ -2735,13 +2738,13 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C104" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="D104" t="s">
-        <v>111</v>
+        <v>38</v>
       </c>
       <c r="E104" t="s">
         <v>146</v>
@@ -2755,7 +2758,7 @@
         <v>130</v>
       </c>
       <c r="C105" t="s">
-        <v>112</v>
+        <v>49</v>
       </c>
       <c r="D105" t="s">
         <v>111</v>
@@ -2772,7 +2775,7 @@
         <v>130</v>
       </c>
       <c r="C106" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D106" t="s">
         <v>111</v>
@@ -2789,7 +2792,7 @@
         <v>130</v>
       </c>
       <c r="C107" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D107" t="s">
         <v>111</v>
@@ -2806,7 +2809,7 @@
         <v>130</v>
       </c>
       <c r="C108" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D108" t="s">
         <v>111</v>
@@ -2823,7 +2826,7 @@
         <v>130</v>
       </c>
       <c r="C109" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D109" t="s">
         <v>111</v>
@@ -2840,7 +2843,7 @@
         <v>130</v>
       </c>
       <c r="C110" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D110" t="s">
         <v>111</v>
@@ -2857,7 +2860,7 @@
         <v>130</v>
       </c>
       <c r="C111" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D111" t="s">
         <v>111</v>
@@ -2874,7 +2877,7 @@
         <v>130</v>
       </c>
       <c r="C112" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D112" t="s">
         <v>111</v>
@@ -2891,7 +2894,7 @@
         <v>130</v>
       </c>
       <c r="C113" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D113" t="s">
         <v>111</v>
@@ -2908,7 +2911,7 @@
         <v>130</v>
       </c>
       <c r="C114" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D114" t="s">
         <v>111</v>
@@ -2925,7 +2928,7 @@
         <v>130</v>
       </c>
       <c r="C115" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D115" t="s">
         <v>111</v>
@@ -2942,7 +2945,7 @@
         <v>130</v>
       </c>
       <c r="C116" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D116" t="s">
         <v>111</v>
@@ -2959,7 +2962,7 @@
         <v>130</v>
       </c>
       <c r="C117" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D117" t="s">
         <v>111</v>
@@ -2976,7 +2979,7 @@
         <v>130</v>
       </c>
       <c r="C118" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D118" t="s">
         <v>111</v>
@@ -2993,7 +2996,7 @@
         <v>130</v>
       </c>
       <c r="C119" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D119" t="s">
         <v>111</v>
@@ -3010,7 +3013,7 @@
         <v>130</v>
       </c>
       <c r="C120" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D120" t="s">
         <v>111</v>
@@ -3027,7 +3030,7 @@
         <v>130</v>
       </c>
       <c r="C121" t="s">
-        <v>51</v>
+        <v>127</v>
       </c>
       <c r="D121" t="s">
         <v>111</v>
@@ -3041,13 +3044,13 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>102</v>
+        <v>130</v>
       </c>
       <c r="C122" t="s">
-        <v>103</v>
+        <v>51</v>
       </c>
       <c r="D122" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="E122" t="s">
         <v>146</v>
@@ -3061,7 +3064,7 @@
         <v>102</v>
       </c>
       <c r="C123" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D123" t="s">
         <v>104</v>
@@ -3078,7 +3081,7 @@
         <v>102</v>
       </c>
       <c r="C124" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D124" t="s">
         <v>104</v>
@@ -3095,7 +3098,7 @@
         <v>102</v>
       </c>
       <c r="C125" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D125" t="s">
         <v>104</v>
@@ -3112,7 +3115,7 @@
         <v>102</v>
       </c>
       <c r="C126" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D126" t="s">
         <v>104</v>
@@ -3129,7 +3132,7 @@
         <v>102</v>
       </c>
       <c r="C127" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D127" t="s">
         <v>104</v>
@@ -3143,13 +3146,13 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="C128" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="D128" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="E128" t="s">
         <v>146</v>
@@ -3163,7 +3166,7 @@
         <v>129</v>
       </c>
       <c r="C129" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D129" t="s">
         <v>95</v>
@@ -3180,7 +3183,7 @@
         <v>129</v>
       </c>
       <c r="C130" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D130" t="s">
         <v>95</v>
@@ -3197,7 +3200,7 @@
         <v>129</v>
       </c>
       <c r="C131" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D131" t="s">
         <v>95</v>
@@ -3214,7 +3217,7 @@
         <v>129</v>
       </c>
       <c r="C132" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D132" t="s">
         <v>95</v>
@@ -3228,13 +3231,13 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>57</v>
+        <v>129</v>
       </c>
       <c r="C133" t="s">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="D133" t="s">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="E133" t="s">
         <v>146</v>
@@ -3248,7 +3251,7 @@
         <v>57</v>
       </c>
       <c r="C134" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D134" t="s">
         <v>59</v>
@@ -3265,7 +3268,7 @@
         <v>57</v>
       </c>
       <c r="C135" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D135" t="s">
         <v>59</v>
@@ -3282,7 +3285,7 @@
         <v>57</v>
       </c>
       <c r="C136" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D136" t="s">
         <v>59</v>
@@ -3299,7 +3302,7 @@
         <v>57</v>
       </c>
       <c r="C137" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D137" t="s">
         <v>59</v>
@@ -3308,7 +3311,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="138" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>137</v>
       </c>
@@ -3316,7 +3319,7 @@
         <v>57</v>
       </c>
       <c r="C138" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D138" t="s">
         <v>59</v>
@@ -3325,7 +3328,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>138</v>
       </c>
@@ -3333,7 +3336,7 @@
         <v>57</v>
       </c>
       <c r="C139" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D139" t="s">
         <v>59</v>
@@ -3350,7 +3353,7 @@
         <v>57</v>
       </c>
       <c r="C140" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D140" t="s">
         <v>59</v>
@@ -3367,7 +3370,7 @@
         <v>57</v>
       </c>
       <c r="C141" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D141" t="s">
         <v>59</v>
@@ -3384,7 +3387,7 @@
         <v>57</v>
       </c>
       <c r="C142" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D142" t="s">
         <v>59</v>
@@ -3401,7 +3404,7 @@
         <v>57</v>
       </c>
       <c r="C143" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D143" t="s">
         <v>59</v>
@@ -3418,7 +3421,7 @@
         <v>57</v>
       </c>
       <c r="C144" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D144" t="s">
         <v>59</v>
@@ -3435,7 +3438,7 @@
         <v>57</v>
       </c>
       <c r="C145" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D145" t="s">
         <v>59</v>
@@ -3452,7 +3455,7 @@
         <v>57</v>
       </c>
       <c r="C146" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D146" t="s">
         <v>59</v>
@@ -3469,7 +3472,7 @@
         <v>57</v>
       </c>
       <c r="C147" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D147" t="s">
         <v>59</v>
@@ -3486,7 +3489,7 @@
         <v>57</v>
       </c>
       <c r="C148" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D148" t="s">
         <v>59</v>
@@ -3503,7 +3506,7 @@
         <v>57</v>
       </c>
       <c r="C149" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D149" t="s">
         <v>59</v>
@@ -3520,7 +3523,7 @@
         <v>57</v>
       </c>
       <c r="C150" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D150" t="s">
         <v>59</v>
@@ -3534,13 +3537,13 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>167</v>
+        <v>57</v>
       </c>
       <c r="C151" t="s">
-        <v>170</v>
+        <v>76</v>
       </c>
       <c r="D151" t="s">
-        <v>169</v>
+        <v>59</v>
       </c>
       <c r="E151" t="s">
         <v>146</v>
@@ -3551,16 +3554,16 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>134</v>
+        <v>167</v>
       </c>
       <c r="C152" t="s">
-        <v>49</v>
+        <v>170</v>
       </c>
       <c r="D152" t="s">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="E152" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
@@ -3571,7 +3574,7 @@
         <v>134</v>
       </c>
       <c r="C153" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D153" t="s">
         <v>147</v>
@@ -3585,13 +3588,13 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>100</v>
+        <v>134</v>
       </c>
       <c r="C154" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="D154" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E154" t="s">
         <v>164</v>
@@ -3605,7 +3608,7 @@
         <v>100</v>
       </c>
       <c r="C155" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D155" t="s">
         <v>148</v>
@@ -3622,7 +3625,7 @@
         <v>100</v>
       </c>
       <c r="C156" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D156" t="s">
         <v>148</v>
@@ -3636,13 +3639,13 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C157" t="s">
-        <v>103</v>
+        <v>37</v>
       </c>
       <c r="D157" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E157" t="s">
         <v>164</v>
@@ -3656,7 +3659,7 @@
         <v>102</v>
       </c>
       <c r="C158" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D158" t="s">
         <v>149</v>
@@ -3673,7 +3676,7 @@
         <v>102</v>
       </c>
       <c r="C159" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D159" t="s">
         <v>149</v>
@@ -3690,7 +3693,7 @@
         <v>102</v>
       </c>
       <c r="C160" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D160" t="s">
         <v>149</v>
@@ -3707,7 +3710,7 @@
         <v>102</v>
       </c>
       <c r="C161" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D161" t="s">
         <v>149</v>
@@ -3724,7 +3727,7 @@
         <v>102</v>
       </c>
       <c r="C162" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D162" t="s">
         <v>149</v>
@@ -3738,13 +3741,13 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="C163" t="s">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D163" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E163" t="s">
         <v>164</v>
@@ -3758,7 +3761,7 @@
         <v>57</v>
       </c>
       <c r="C164" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D164" t="s">
         <v>150</v>
@@ -3775,7 +3778,7 @@
         <v>57</v>
       </c>
       <c r="C165" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D165" t="s">
         <v>150</v>
@@ -3792,7 +3795,7 @@
         <v>57</v>
       </c>
       <c r="C166" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D166" t="s">
         <v>150</v>
@@ -3809,7 +3812,7 @@
         <v>57</v>
       </c>
       <c r="C167" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D167" t="s">
         <v>150</v>
@@ -3826,7 +3829,7 @@
         <v>57</v>
       </c>
       <c r="C168" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D168" t="s">
         <v>150</v>
@@ -3843,7 +3846,7 @@
         <v>57</v>
       </c>
       <c r="C169" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D169" t="s">
         <v>150</v>
@@ -3860,7 +3863,7 @@
         <v>57</v>
       </c>
       <c r="C170" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D170" t="s">
         <v>150</v>
@@ -3877,7 +3880,7 @@
         <v>57</v>
       </c>
       <c r="C171" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D171" t="s">
         <v>150</v>
@@ -3894,7 +3897,7 @@
         <v>57</v>
       </c>
       <c r="C172" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D172" t="s">
         <v>150</v>
@@ -3911,7 +3914,7 @@
         <v>57</v>
       </c>
       <c r="C173" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D173" t="s">
         <v>150</v>
@@ -3928,7 +3931,7 @@
         <v>57</v>
       </c>
       <c r="C174" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D174" t="s">
         <v>150</v>
@@ -3945,7 +3948,7 @@
         <v>57</v>
       </c>
       <c r="C175" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D175" t="s">
         <v>150</v>
@@ -3962,7 +3965,7 @@
         <v>57</v>
       </c>
       <c r="C176" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D176" t="s">
         <v>150</v>
@@ -3979,7 +3982,7 @@
         <v>57</v>
       </c>
       <c r="C177" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D177" t="s">
         <v>150</v>
@@ -3996,7 +3999,7 @@
         <v>57</v>
       </c>
       <c r="C178" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D178" t="s">
         <v>150</v>
@@ -4013,7 +4016,7 @@
         <v>57</v>
       </c>
       <c r="C179" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D179" t="s">
         <v>150</v>
@@ -4030,7 +4033,7 @@
         <v>57</v>
       </c>
       <c r="C180" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D180" t="s">
         <v>150</v>
@@ -4044,13 +4047,13 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="C181" t="s">
-        <v>22</v>
+        <v>76</v>
       </c>
       <c r="D181" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E181" t="s">
         <v>164</v>
@@ -4061,13 +4064,13 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="C182" t="s">
-        <v>89</v>
+        <v>22</v>
       </c>
       <c r="D182" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E182" t="s">
         <v>164</v>
@@ -4081,7 +4084,7 @@
         <v>88</v>
       </c>
       <c r="C183" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D183" t="s">
         <v>152</v>
@@ -4098,7 +4101,7 @@
         <v>88</v>
       </c>
       <c r="C184" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D184" t="s">
         <v>152</v>
@@ -4115,7 +4118,7 @@
         <v>88</v>
       </c>
       <c r="C185" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D185" t="s">
         <v>152</v>
@@ -4129,13 +4132,13 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
-        <v>3</v>
+        <v>88</v>
       </c>
       <c r="C186" t="s">
-        <v>4</v>
+        <v>93</v>
       </c>
       <c r="D186" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E186" t="s">
         <v>164</v>
@@ -4149,7 +4152,7 @@
         <v>3</v>
       </c>
       <c r="C187" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D187" t="s">
         <v>153</v>
@@ -4166,7 +4169,7 @@
         <v>3</v>
       </c>
       <c r="C188" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D188" t="s">
         <v>153</v>
@@ -4183,7 +4186,7 @@
         <v>3</v>
       </c>
       <c r="C189" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D189" t="s">
         <v>153</v>
@@ -4200,7 +4203,7 @@
         <v>3</v>
       </c>
       <c r="C190" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D190" t="s">
         <v>153</v>
@@ -4217,7 +4220,7 @@
         <v>3</v>
       </c>
       <c r="C191" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D191" t="s">
         <v>153</v>
@@ -4234,7 +4237,7 @@
         <v>3</v>
       </c>
       <c r="C192" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D192" t="s">
         <v>153</v>
@@ -4251,7 +4254,7 @@
         <v>3</v>
       </c>
       <c r="C193" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D193" t="s">
         <v>153</v>
@@ -4268,7 +4271,7 @@
         <v>3</v>
       </c>
       <c r="C194" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D194" t="s">
         <v>153</v>
@@ -4285,7 +4288,7 @@
         <v>3</v>
       </c>
       <c r="C195" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D195" t="s">
         <v>153</v>
@@ -4299,13 +4302,13 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="C196" t="s">
-        <v>81</v>
+        <v>14</v>
       </c>
       <c r="D196" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E196" t="s">
         <v>164</v>
@@ -4319,7 +4322,7 @@
         <v>80</v>
       </c>
       <c r="C197" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D197" t="s">
         <v>154</v>
@@ -4336,7 +4339,7 @@
         <v>80</v>
       </c>
       <c r="C198" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D198" t="s">
         <v>154</v>
@@ -4353,7 +4356,7 @@
         <v>80</v>
       </c>
       <c r="C199" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D199" t="s">
         <v>154</v>
@@ -4370,7 +4373,7 @@
         <v>80</v>
       </c>
       <c r="C200" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D200" t="s">
         <v>154</v>
@@ -4387,7 +4390,7 @@
         <v>80</v>
       </c>
       <c r="C201" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D201" t="s">
         <v>154</v>
@@ -4401,13 +4404,13 @@
         <v>201</v>
       </c>
       <c r="B202" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="C202" t="s">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="D202" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E202" t="s">
         <v>164</v>
@@ -4418,13 +4421,13 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="C203" t="s">
-        <v>41</v>
+        <v>190</v>
       </c>
       <c r="D203" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E203" t="s">
         <v>164</v>
@@ -4438,7 +4441,7 @@
         <v>39</v>
       </c>
       <c r="C204" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D204" t="s">
         <v>155</v>
@@ -4455,7 +4458,7 @@
         <v>39</v>
       </c>
       <c r="C205" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D205" t="s">
         <v>155</v>
@@ -4472,7 +4475,7 @@
         <v>39</v>
       </c>
       <c r="C206" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D206" t="s">
         <v>155</v>
@@ -4489,7 +4492,7 @@
         <v>39</v>
       </c>
       <c r="C207" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D207" t="s">
         <v>155</v>
@@ -4506,7 +4509,7 @@
         <v>39</v>
       </c>
       <c r="C208" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D208" t="s">
         <v>155</v>
@@ -4523,7 +4526,7 @@
         <v>39</v>
       </c>
       <c r="C209" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D209" t="s">
         <v>155</v>
@@ -4540,7 +4543,7 @@
         <v>39</v>
       </c>
       <c r="C210" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D210" t="s">
         <v>155</v>
@@ -4554,13 +4557,13 @@
         <v>210</v>
       </c>
       <c r="B211" t="s">
-        <v>129</v>
+        <v>39</v>
       </c>
       <c r="C211" t="s">
-        <v>94</v>
+        <v>47</v>
       </c>
       <c r="D211" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E211" t="s">
         <v>164</v>
@@ -4571,13 +4574,13 @@
         <v>211</v>
       </c>
       <c r="B212" t="s">
-        <v>129</v>
+        <v>39</v>
       </c>
       <c r="C212" t="s">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="D212" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E212" t="s">
         <v>164</v>
@@ -4591,7 +4594,7 @@
         <v>129</v>
       </c>
       <c r="C213" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D213" t="s">
         <v>156</v>
@@ -4608,7 +4611,7 @@
         <v>129</v>
       </c>
       <c r="C214" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D214" t="s">
         <v>156</v>
@@ -4625,7 +4628,7 @@
         <v>129</v>
       </c>
       <c r="C215" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D215" t="s">
         <v>156</v>
@@ -4639,13 +4642,13 @@
         <v>215</v>
       </c>
       <c r="B216" t="s">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="C216" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="D216" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E216" t="s">
         <v>164</v>
@@ -4656,13 +4659,13 @@
         <v>216</v>
       </c>
       <c r="B217" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C217" t="s">
-        <v>4</v>
+        <v>99</v>
       </c>
       <c r="D217" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E217" t="s">
         <v>164</v>
@@ -4673,13 +4676,13 @@
         <v>217</v>
       </c>
       <c r="B218" t="s">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c r="C218" t="s">
-        <v>6</v>
+        <v>78</v>
       </c>
       <c r="D218" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E218" t="s">
         <v>164</v>
@@ -4693,7 +4696,7 @@
         <v>133</v>
       </c>
       <c r="C219" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D219" t="s">
         <v>158</v>
@@ -4710,7 +4713,7 @@
         <v>133</v>
       </c>
       <c r="C220" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D220" t="s">
         <v>158</v>
@@ -4727,7 +4730,7 @@
         <v>133</v>
       </c>
       <c r="C221" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D221" t="s">
         <v>158</v>
@@ -4744,7 +4747,7 @@
         <v>133</v>
       </c>
       <c r="C222" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D222" t="s">
         <v>158</v>
@@ -4761,7 +4764,7 @@
         <v>133</v>
       </c>
       <c r="C223" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D223" t="s">
         <v>158</v>
@@ -4778,7 +4781,7 @@
         <v>133</v>
       </c>
       <c r="C224" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D224" t="s">
         <v>158</v>
@@ -4795,7 +4798,7 @@
         <v>133</v>
       </c>
       <c r="C225" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D225" t="s">
         <v>158</v>
@@ -4812,7 +4815,7 @@
         <v>133</v>
       </c>
       <c r="C226" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D226" t="s">
         <v>158</v>
@@ -4826,19 +4829,16 @@
         <v>226</v>
       </c>
       <c r="B227" t="s">
-        <v>53</v>
+        <v>133</v>
       </c>
       <c r="C227" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="D227" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E227" t="s">
         <v>164</v>
-      </c>
-      <c r="L227" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="228" spans="1:12" x14ac:dyDescent="0.25">
@@ -4846,19 +4846,16 @@
         <v>227</v>
       </c>
       <c r="B228" t="s">
-        <v>53</v>
+        <v>133</v>
       </c>
       <c r="C228" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="D228" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E228" t="s">
         <v>164</v>
-      </c>
-      <c r="L228" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="229" spans="1:12" x14ac:dyDescent="0.25">
@@ -4866,19 +4863,19 @@
         <v>228</v>
       </c>
       <c r="B229" t="s">
-        <v>128</v>
+        <v>53</v>
       </c>
       <c r="C229" t="s">
-        <v>179</v>
+        <v>54</v>
       </c>
       <c r="D229" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E229" t="s">
         <v>164</v>
       </c>
       <c r="L229" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="230" spans="1:12" x14ac:dyDescent="0.25">
@@ -4886,19 +4883,19 @@
         <v>229</v>
       </c>
       <c r="B230" t="s">
-        <v>128</v>
+        <v>53</v>
       </c>
       <c r="C230" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="D230" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E230" t="s">
         <v>164</v>
       </c>
       <c r="L230" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="231" spans="1:12" x14ac:dyDescent="0.25">
@@ -4909,13 +4906,16 @@
         <v>128</v>
       </c>
       <c r="C231" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="D231" t="s">
         <v>160</v>
       </c>
       <c r="E231" t="s">
         <v>164</v>
+      </c>
+      <c r="L231" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="232" spans="1:12" x14ac:dyDescent="0.25">
@@ -4926,13 +4926,16 @@
         <v>128</v>
       </c>
       <c r="C232" t="s">
-        <v>180</v>
+        <v>16</v>
       </c>
       <c r="D232" t="s">
         <v>160</v>
       </c>
       <c r="E232" t="s">
         <v>164</v>
+      </c>
+      <c r="L232" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="233" spans="1:12" x14ac:dyDescent="0.25">
@@ -4943,7 +4946,7 @@
         <v>128</v>
       </c>
       <c r="C233" t="s">
-        <v>17</v>
+        <v>185</v>
       </c>
       <c r="D233" t="s">
         <v>160</v>
@@ -4960,7 +4963,7 @@
         <v>128</v>
       </c>
       <c r="C234" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D234" t="s">
         <v>160</v>
@@ -4977,7 +4980,7 @@
         <v>128</v>
       </c>
       <c r="C235" t="s">
-        <v>181</v>
+        <v>17</v>
       </c>
       <c r="D235" t="s">
         <v>160</v>
@@ -4994,7 +4997,7 @@
         <v>128</v>
       </c>
       <c r="C236" t="s">
-        <v>18</v>
+        <v>186</v>
       </c>
       <c r="D236" t="s">
         <v>160</v>
@@ -5011,7 +5014,7 @@
         <v>128</v>
       </c>
       <c r="C237" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="D237" t="s">
         <v>160</v>
@@ -5028,7 +5031,7 @@
         <v>128</v>
       </c>
       <c r="C238" t="s">
-        <v>182</v>
+        <v>18</v>
       </c>
       <c r="D238" t="s">
         <v>160</v>
@@ -5045,7 +5048,7 @@
         <v>128</v>
       </c>
       <c r="C239" t="s">
-        <v>19</v>
+        <v>187</v>
       </c>
       <c r="D239" t="s">
         <v>160</v>
@@ -5062,7 +5065,7 @@
         <v>128</v>
       </c>
       <c r="C240" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="D240" t="s">
         <v>160</v>
@@ -5079,7 +5082,7 @@
         <v>128</v>
       </c>
       <c r="C241" t="s">
-        <v>183</v>
+        <v>19</v>
       </c>
       <c r="D241" t="s">
         <v>160</v>
@@ -5096,7 +5099,7 @@
         <v>128</v>
       </c>
       <c r="C242" t="s">
-        <v>20</v>
+        <v>188</v>
       </c>
       <c r="D242" t="s">
         <v>160</v>
@@ -5113,7 +5116,7 @@
         <v>128</v>
       </c>
       <c r="C243" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D243" t="s">
         <v>160</v>
@@ -5127,13 +5130,13 @@
         <v>243</v>
       </c>
       <c r="B244" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C244" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D244" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E244" t="s">
         <v>164</v>
@@ -5144,13 +5147,13 @@
         <v>244</v>
       </c>
       <c r="B245" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C245" t="s">
-        <v>27</v>
+        <v>184</v>
       </c>
       <c r="D245" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E245" t="s">
         <v>164</v>
@@ -5164,7 +5167,7 @@
         <v>131</v>
       </c>
       <c r="C246" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D246" t="s">
         <v>161</v>
@@ -5181,7 +5184,7 @@
         <v>131</v>
       </c>
       <c r="C247" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D247" t="s">
         <v>161</v>
@@ -5198,7 +5201,7 @@
         <v>131</v>
       </c>
       <c r="C248" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D248" t="s">
         <v>161</v>
@@ -5215,7 +5218,7 @@
         <v>131</v>
       </c>
       <c r="C249" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D249" t="s">
         <v>161</v>
@@ -5232,7 +5235,7 @@
         <v>131</v>
       </c>
       <c r="C250" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D250" t="s">
         <v>161</v>
@@ -5249,7 +5252,7 @@
         <v>131</v>
       </c>
       <c r="C251" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D251" t="s">
         <v>161</v>
@@ -5266,7 +5269,7 @@
         <v>131</v>
       </c>
       <c r="C252" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D252" t="s">
         <v>161</v>
@@ -5283,7 +5286,7 @@
         <v>131</v>
       </c>
       <c r="C253" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D253" t="s">
         <v>161</v>
@@ -5300,7 +5303,7 @@
         <v>131</v>
       </c>
       <c r="C254" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D254" t="s">
         <v>161</v>
@@ -5317,7 +5320,7 @@
         <v>131</v>
       </c>
       <c r="C255" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D255" t="s">
         <v>161</v>
@@ -5331,13 +5334,13 @@
         <v>255</v>
       </c>
       <c r="B256" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C256" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D256" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E256" t="s">
         <v>164</v>
@@ -5348,13 +5351,13 @@
         <v>256</v>
       </c>
       <c r="B257" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C257" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D257" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E257" t="s">
         <v>164</v>
@@ -5368,7 +5371,7 @@
         <v>132</v>
       </c>
       <c r="C258" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D258" t="s">
         <v>162</v>
@@ -5385,7 +5388,7 @@
         <v>132</v>
       </c>
       <c r="C259" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D259" t="s">
         <v>162</v>
@@ -5402,7 +5405,7 @@
         <v>132</v>
       </c>
       <c r="C260" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D260" t="s">
         <v>162</v>
@@ -5419,7 +5422,7 @@
         <v>132</v>
       </c>
       <c r="C261" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D261" t="s">
         <v>162</v>
@@ -5436,7 +5439,7 @@
         <v>132</v>
       </c>
       <c r="C262" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D262" t="s">
         <v>162</v>
@@ -5453,7 +5456,7 @@
         <v>132</v>
       </c>
       <c r="C263" t="s">
-        <v>189</v>
+        <v>45</v>
       </c>
       <c r="D263" t="s">
         <v>162</v>
@@ -5470,7 +5473,7 @@
         <v>132</v>
       </c>
       <c r="C264" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D264" t="s">
         <v>162</v>
@@ -5484,13 +5487,13 @@
         <v>264</v>
       </c>
       <c r="B265" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C265" t="s">
-        <v>49</v>
+        <v>189</v>
       </c>
       <c r="D265" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E265" t="s">
         <v>164</v>
@@ -5501,13 +5504,13 @@
         <v>265</v>
       </c>
       <c r="B266" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C266" t="s">
-        <v>112</v>
+        <v>48</v>
       </c>
       <c r="D266" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E266" t="s">
         <v>164</v>
@@ -5521,7 +5524,7 @@
         <v>130</v>
       </c>
       <c r="C267" t="s">
-        <v>113</v>
+        <v>49</v>
       </c>
       <c r="D267" t="s">
         <v>163</v>
@@ -5538,7 +5541,7 @@
         <v>130</v>
       </c>
       <c r="C268" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D268" t="s">
         <v>163</v>
@@ -5555,7 +5558,7 @@
         <v>130</v>
       </c>
       <c r="C269" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D269" t="s">
         <v>163</v>
@@ -5572,7 +5575,7 @@
         <v>130</v>
       </c>
       <c r="C270" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D270" t="s">
         <v>163</v>
@@ -5589,7 +5592,7 @@
         <v>130</v>
       </c>
       <c r="C271" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D271" t="s">
         <v>163</v>
@@ -5606,7 +5609,7 @@
         <v>130</v>
       </c>
       <c r="C272" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D272" t="s">
         <v>163</v>
@@ -5623,7 +5626,7 @@
         <v>130</v>
       </c>
       <c r="C273" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D273" t="s">
         <v>163</v>
@@ -5640,7 +5643,7 @@
         <v>130</v>
       </c>
       <c r="C274" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D274" t="s">
         <v>163</v>
@@ -5657,7 +5660,7 @@
         <v>130</v>
       </c>
       <c r="C275" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D275" t="s">
         <v>163</v>
@@ -5674,7 +5677,7 @@
         <v>130</v>
       </c>
       <c r="C276" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D276" t="s">
         <v>163</v>
@@ -5691,7 +5694,7 @@
         <v>130</v>
       </c>
       <c r="C277" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D277" t="s">
         <v>163</v>
@@ -5708,7 +5711,7 @@
         <v>130</v>
       </c>
       <c r="C278" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D278" t="s">
         <v>163</v>
@@ -5725,7 +5728,7 @@
         <v>130</v>
       </c>
       <c r="C279" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D279" t="s">
         <v>163</v>
@@ -5742,7 +5745,7 @@
         <v>130</v>
       </c>
       <c r="C280" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D280" t="s">
         <v>163</v>
@@ -5759,7 +5762,7 @@
         <v>130</v>
       </c>
       <c r="C281" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D281" t="s">
         <v>163</v>
@@ -5776,7 +5779,7 @@
         <v>130</v>
       </c>
       <c r="C282" t="s">
-        <v>51</v>
+        <v>126</v>
       </c>
       <c r="D282" t="s">
         <v>163</v>
@@ -5790,13 +5793,13 @@
         <v>282</v>
       </c>
       <c r="B283" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C283" t="s">
-        <v>25</v>
+        <v>127</v>
       </c>
       <c r="D283" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E283" t="s">
         <v>164</v>
@@ -5807,13 +5810,13 @@
         <v>283</v>
       </c>
       <c r="B284" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C284" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="D284" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E284" t="s">
         <v>164</v>
@@ -5827,7 +5830,7 @@
         <v>135</v>
       </c>
       <c r="C285" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D285" t="s">
         <v>165</v>
@@ -5844,7 +5847,7 @@
         <v>135</v>
       </c>
       <c r="C286" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D286" t="s">
         <v>165</v>
@@ -5861,7 +5864,7 @@
         <v>135</v>
       </c>
       <c r="C287" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D287" t="s">
         <v>165</v>
@@ -5878,7 +5881,7 @@
         <v>135</v>
       </c>
       <c r="C288" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D288" t="s">
         <v>165</v>
@@ -5895,7 +5898,7 @@
         <v>135</v>
       </c>
       <c r="C289" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D289" t="s">
         <v>165</v>
@@ -5912,7 +5915,7 @@
         <v>135</v>
       </c>
       <c r="C290" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D290" t="s">
         <v>165</v>
@@ -5929,7 +5932,7 @@
         <v>135</v>
       </c>
       <c r="C291" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D291" t="s">
         <v>165</v>
@@ -5943,13 +5946,13 @@
         <v>291</v>
       </c>
       <c r="B292" t="s">
-        <v>24</v>
+        <v>135</v>
       </c>
       <c r="C292" t="s">
-        <v>136</v>
+        <v>33</v>
       </c>
       <c r="D292" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E292" t="s">
         <v>164</v>
@@ -5960,13 +5963,13 @@
         <v>292</v>
       </c>
       <c r="B293" t="s">
-        <v>24</v>
+        <v>135</v>
       </c>
       <c r="C293" t="s">
-        <v>137</v>
+        <v>34</v>
       </c>
       <c r="D293" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E293" t="s">
         <v>164</v>
@@ -5980,7 +5983,7 @@
         <v>24</v>
       </c>
       <c r="C294" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D294" t="s">
         <v>166</v>
@@ -5997,7 +6000,7 @@
         <v>24</v>
       </c>
       <c r="C295" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D295" t="s">
         <v>166</v>
@@ -6014,7 +6017,7 @@
         <v>24</v>
       </c>
       <c r="C296" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D296" t="s">
         <v>166</v>
@@ -6031,7 +6034,7 @@
         <v>24</v>
       </c>
       <c r="C297" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D297" t="s">
         <v>166</v>
@@ -6048,7 +6051,7 @@
         <v>24</v>
       </c>
       <c r="C298" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D298" t="s">
         <v>166</v>
@@ -6065,7 +6068,7 @@
         <v>24</v>
       </c>
       <c r="C299" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D299" t="s">
         <v>166</v>
@@ -6082,7 +6085,7 @@
         <v>24</v>
       </c>
       <c r="C300" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D300" t="s">
         <v>166</v>
@@ -6096,13 +6099,13 @@
         <v>300</v>
       </c>
       <c r="B301" t="s">
-        <v>167</v>
+        <v>24</v>
       </c>
       <c r="C301" t="s">
-        <v>170</v>
+        <v>143</v>
       </c>
       <c r="D301" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E301" t="s">
         <v>164</v>
@@ -6113,16 +6116,16 @@
         <v>301</v>
       </c>
       <c r="B302" t="s">
-        <v>173</v>
+        <v>24</v>
       </c>
       <c r="C302" t="s">
-        <v>174</v>
+        <v>144</v>
       </c>
       <c r="D302" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="E302" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.25">
@@ -6130,22 +6133,56 @@
         <v>302</v>
       </c>
       <c r="B303" t="s">
+        <v>167</v>
+      </c>
+      <c r="C303" t="s">
+        <v>170</v>
+      </c>
+      <c r="D303" t="s">
+        <v>168</v>
+      </c>
+      <c r="E303" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A304" s="1">
+        <v>303</v>
+      </c>
+      <c r="B304" t="s">
         <v>173</v>
       </c>
-      <c r="C303" t="s">
+      <c r="C304" t="s">
         <v>174</v>
       </c>
-      <c r="D303" t="s">
+      <c r="D304" t="s">
+        <v>175</v>
+      </c>
+      <c r="E304" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A305" s="1">
+        <v>304</v>
+      </c>
+      <c r="B305" t="s">
+        <v>173</v>
+      </c>
+      <c r="C305" t="s">
+        <v>174</v>
+      </c>
+      <c r="D305" t="s">
         <v>176</v>
       </c>
-      <c r="E303" t="s">
+      <c r="E305" t="s">
         <v>164</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E303" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E301">
-      <sortCondition ref="A1:A301"/>
+  <autoFilter ref="A1:E305" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E305">
+      <sortCondition ref="A1:A305"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
